--- a/output.xlsx
+++ b/output.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,6 +463,16 @@
           <t>MONTANT_A_PAYER</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Validation_Status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -510,6 +520,208 @@
           <t>5845.33</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FAFPLP_5_20260707_200792_001296_86.PDF</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>200792</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>07/07/26</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>001296</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>49.44</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>9.89</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>59.33</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FAFPLP_A_20260706_399535_001343_86.PDF</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>399535</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>06/07/26</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>001343</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>21.05</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25.26</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FAFPLP_E_20260706_657058_001169_86.PDF</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>657058</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>06/07/26</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>001169</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>84.50</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>16.90</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>101.40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FAFPLP_R_20260702_915189_001923_86.PDF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>915189</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>02/07/26</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>001923</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>32.50</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -522,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +778,16 @@
           <t>Montant_a_payer</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Validation_Status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -608,6 +830,12 @@
           <t>362.42</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
